--- a/admin.xlsx
+++ b/admin.xlsx
@@ -357,7 +357,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -385,6 +386,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="OAmSCFu0LQ4lQWR1IBRvYfOjfxJpwjDyZffGzax5Jm0fHwbjsQfLNHZU7pFjeKFbRjzvBBQrubMJfIrx0/hzDw==" saltValue="FLoQATX82uuQQZ0EShwr5Q==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>